--- a/artfynd/A 61045-2025 artfynd.xlsx
+++ b/artfynd/A 61045-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131389079</v>
       </c>
       <c r="B2" t="n">
-        <v>91834</v>
+        <v>91836</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -771,7 +771,7 @@
         <v>131389092</v>
       </c>
       <c r="B3" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -870,10 +870,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131389095</v>
+        <v>131389080</v>
       </c>
       <c r="B4" t="n">
-        <v>79246</v>
+        <v>91836</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -881,23 +881,19 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -905,10 +901,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>459006</v>
+        <v>458981</v>
       </c>
       <c r="R4" t="n">
-        <v>7080327</v>
+        <v>7080328</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -941,11 +937,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2026-02-27</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -972,10 +963,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131389080</v>
+        <v>131389095</v>
       </c>
       <c r="B5" t="n">
-        <v>91834</v>
+        <v>79248</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -983,19 +974,23 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1003,10 +998,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>458981</v>
+        <v>459006</v>
       </c>
       <c r="R5" t="n">
-        <v>7080328</v>
+        <v>7080327</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1039,6 +1034,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1068,7 +1068,7 @@
         <v>131389093</v>
       </c>
       <c r="B6" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1170,7 +1170,7 @@
         <v>131389094</v>
       </c>
       <c r="B7" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1272,7 +1272,7 @@
         <v>131389078</v>
       </c>
       <c r="B8" t="n">
-        <v>91834</v>
+        <v>91836</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 61045-2025 artfynd.xlsx
+++ b/artfynd/A 61045-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131389079</v>
+        <v>131389092</v>
       </c>
       <c r="B2" t="n">
-        <v>91836</v>
+        <v>79249</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,19 +686,23 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -706,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>459042</v>
+        <v>459047</v>
       </c>
       <c r="R2" t="n">
-        <v>7080319</v>
+        <v>7080320</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -742,6 +746,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -768,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131389092</v>
+        <v>131389079</v>
       </c>
       <c r="B3" t="n">
-        <v>79248</v>
+        <v>91837</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -779,23 +788,19 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -803,10 +808,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>459047</v>
+        <v>459042</v>
       </c>
       <c r="R3" t="n">
-        <v>7080320</v>
+        <v>7080319</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -839,11 +844,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2026-02-27</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -870,10 +870,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131389080</v>
+        <v>131389095</v>
       </c>
       <c r="B4" t="n">
-        <v>91836</v>
+        <v>79249</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -881,19 +881,23 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -901,10 +905,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>458981</v>
+        <v>459006</v>
       </c>
       <c r="R4" t="n">
-        <v>7080328</v>
+        <v>7080327</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -937,6 +941,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -963,10 +972,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131389095</v>
+        <v>131389080</v>
       </c>
       <c r="B5" t="n">
-        <v>79248</v>
+        <v>91837</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -974,23 +983,19 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -998,10 +1003,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>459006</v>
+        <v>458981</v>
       </c>
       <c r="R5" t="n">
-        <v>7080327</v>
+        <v>7080328</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1034,11 +1039,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2026-02-27</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1068,7 +1068,7 @@
         <v>131389093</v>
       </c>
       <c r="B6" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1170,7 +1170,7 @@
         <v>131389094</v>
       </c>
       <c r="B7" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1272,7 +1272,7 @@
         <v>131389078</v>
       </c>
       <c r="B8" t="n">
-        <v>91836</v>
+        <v>91837</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 61045-2025 artfynd.xlsx
+++ b/artfynd/A 61045-2025 artfynd.xlsx
@@ -870,10 +870,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131389095</v>
+        <v>131389080</v>
       </c>
       <c r="B4" t="n">
-        <v>79249</v>
+        <v>91837</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -881,23 +881,19 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -905,10 +901,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>459006</v>
+        <v>458981</v>
       </c>
       <c r="R4" t="n">
-        <v>7080327</v>
+        <v>7080328</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -941,11 +937,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2026-02-27</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -972,10 +963,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131389080</v>
+        <v>131389095</v>
       </c>
       <c r="B5" t="n">
-        <v>91837</v>
+        <v>79249</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -983,19 +974,23 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1003,10 +998,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>458981</v>
+        <v>459006</v>
       </c>
       <c r="R5" t="n">
-        <v>7080328</v>
+        <v>7080327</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1039,6 +1034,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 61045-2025 artfynd.xlsx
+++ b/artfynd/A 61045-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131389092</v>
       </c>
       <c r="B2" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>131389079</v>
       </c>
       <c r="B3" t="n">
-        <v>91837</v>
+        <v>91838</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -873,7 +873,7 @@
         <v>131389080</v>
       </c>
       <c r="B4" t="n">
-        <v>91837</v>
+        <v>91838</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -966,7 +966,7 @@
         <v>131389095</v>
       </c>
       <c r="B5" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1068,7 +1068,7 @@
         <v>131389093</v>
       </c>
       <c r="B6" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1170,7 +1170,7 @@
         <v>131389094</v>
       </c>
       <c r="B7" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1272,7 +1272,7 @@
         <v>131389078</v>
       </c>
       <c r="B8" t="n">
-        <v>91837</v>
+        <v>91838</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 61045-2025 artfynd.xlsx
+++ b/artfynd/A 61045-2025 artfynd.xlsx
@@ -870,10 +870,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131389080</v>
+        <v>131389095</v>
       </c>
       <c r="B4" t="n">
-        <v>91838</v>
+        <v>79250</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -881,19 +881,23 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -901,10 +905,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>458981</v>
+        <v>459006</v>
       </c>
       <c r="R4" t="n">
-        <v>7080328</v>
+        <v>7080327</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -937,6 +941,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -963,10 +972,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131389095</v>
+        <v>131389080</v>
       </c>
       <c r="B5" t="n">
-        <v>79250</v>
+        <v>91838</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -974,23 +983,19 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -998,10 +1003,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>459006</v>
+        <v>458981</v>
       </c>
       <c r="R5" t="n">
-        <v>7080327</v>
+        <v>7080328</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1034,11 +1039,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2026-02-27</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 61045-2025 artfynd.xlsx
+++ b/artfynd/A 61045-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131389092</v>
+        <v>131389079</v>
       </c>
       <c r="B2" t="n">
-        <v>79250</v>
+        <v>91841</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,23 +686,19 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -710,10 +706,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>459047</v>
+        <v>459042</v>
       </c>
       <c r="R2" t="n">
-        <v>7080320</v>
+        <v>7080319</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -746,11 +742,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2026-02-27</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,10 +768,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131389079</v>
+        <v>131389092</v>
       </c>
       <c r="B3" t="n">
-        <v>91838</v>
+        <v>79253</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -788,19 +779,23 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -808,10 +803,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>459042</v>
+        <v>459047</v>
       </c>
       <c r="R3" t="n">
-        <v>7080319</v>
+        <v>7080320</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -844,6 +839,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -870,10 +870,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131389095</v>
+        <v>131389080</v>
       </c>
       <c r="B4" t="n">
-        <v>79250</v>
+        <v>91841</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -881,23 +881,19 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -905,10 +901,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>459006</v>
+        <v>458981</v>
       </c>
       <c r="R4" t="n">
-        <v>7080327</v>
+        <v>7080328</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -941,11 +937,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2026-02-27</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -972,10 +963,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131389080</v>
+        <v>131389095</v>
       </c>
       <c r="B5" t="n">
-        <v>91838</v>
+        <v>79253</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -983,19 +974,23 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1003,10 +998,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>458981</v>
+        <v>459006</v>
       </c>
       <c r="R5" t="n">
-        <v>7080328</v>
+        <v>7080327</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1039,6 +1034,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1068,7 +1068,7 @@
         <v>131389093</v>
       </c>
       <c r="B6" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1170,7 +1170,7 @@
         <v>131389094</v>
       </c>
       <c r="B7" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1272,7 +1272,7 @@
         <v>131389078</v>
       </c>
       <c r="B8" t="n">
-        <v>91838</v>
+        <v>91841</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 61045-2025 artfynd.xlsx
+++ b/artfynd/A 61045-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131389079</v>
       </c>
       <c r="B2" t="n">
-        <v>91841</v>
+        <v>91842</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -771,7 +771,7 @@
         <v>131389092</v>
       </c>
       <c r="B3" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -873,7 +873,7 @@
         <v>131389080</v>
       </c>
       <c r="B4" t="n">
-        <v>91841</v>
+        <v>91842</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -966,7 +966,7 @@
         <v>131389095</v>
       </c>
       <c r="B5" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1068,7 +1068,7 @@
         <v>131389093</v>
       </c>
       <c r="B6" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1170,7 +1170,7 @@
         <v>131389094</v>
       </c>
       <c r="B7" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1272,7 +1272,7 @@
         <v>131389078</v>
       </c>
       <c r="B8" t="n">
-        <v>91841</v>
+        <v>91842</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 61045-2025 artfynd.xlsx
+++ b/artfynd/A 61045-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131389079</v>
+        <v>131389092</v>
       </c>
       <c r="B2" t="n">
-        <v>91842</v>
+        <v>79260</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,19 +686,23 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -706,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>459042</v>
+        <v>459047</v>
       </c>
       <c r="R2" t="n">
-        <v>7080319</v>
+        <v>7080320</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -742,6 +746,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -768,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131389092</v>
+        <v>131389079</v>
       </c>
       <c r="B3" t="n">
-        <v>79254</v>
+        <v>91848</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -779,23 +788,19 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -803,10 +808,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>459047</v>
+        <v>459042</v>
       </c>
       <c r="R3" t="n">
-        <v>7080320</v>
+        <v>7080319</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -839,11 +844,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2026-02-27</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -870,10 +870,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131389080</v>
+        <v>131389095</v>
       </c>
       <c r="B4" t="n">
-        <v>91842</v>
+        <v>79260</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -881,19 +881,23 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -901,10 +905,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>458981</v>
+        <v>459006</v>
       </c>
       <c r="R4" t="n">
-        <v>7080328</v>
+        <v>7080327</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -937,6 +941,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -963,10 +972,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131389095</v>
+        <v>131389080</v>
       </c>
       <c r="B5" t="n">
-        <v>79254</v>
+        <v>91848</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -974,23 +983,19 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -998,10 +1003,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>459006</v>
+        <v>458981</v>
       </c>
       <c r="R5" t="n">
-        <v>7080327</v>
+        <v>7080328</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1034,11 +1039,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2026-02-27</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1068,7 +1068,7 @@
         <v>131389093</v>
       </c>
       <c r="B6" t="n">
-        <v>79254</v>
+        <v>79260</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1170,7 +1170,7 @@
         <v>131389094</v>
       </c>
       <c r="B7" t="n">
-        <v>79254</v>
+        <v>79260</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1272,7 +1272,7 @@
         <v>131389078</v>
       </c>
       <c r="B8" t="n">
-        <v>91842</v>
+        <v>91848</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 61045-2025 artfynd.xlsx
+++ b/artfynd/A 61045-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131389092</v>
+        <v>131389079</v>
       </c>
       <c r="B2" t="n">
-        <v>79260</v>
+        <v>91848</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,23 +686,19 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -710,10 +706,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>459047</v>
+        <v>459042</v>
       </c>
       <c r="R2" t="n">
-        <v>7080320</v>
+        <v>7080319</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -746,11 +742,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2026-02-27</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,10 +768,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131389079</v>
+        <v>131389092</v>
       </c>
       <c r="B3" t="n">
-        <v>91848</v>
+        <v>79260</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -788,19 +779,23 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -808,10 +803,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>459042</v>
+        <v>459047</v>
       </c>
       <c r="R3" t="n">
-        <v>7080319</v>
+        <v>7080320</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -844,6 +839,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -870,10 +870,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131389095</v>
+        <v>131389080</v>
       </c>
       <c r="B4" t="n">
-        <v>79260</v>
+        <v>91848</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -881,23 +881,19 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -905,10 +901,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>459006</v>
+        <v>458981</v>
       </c>
       <c r="R4" t="n">
-        <v>7080327</v>
+        <v>7080328</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -941,11 +937,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2026-02-27</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -972,10 +963,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131389080</v>
+        <v>131389095</v>
       </c>
       <c r="B5" t="n">
-        <v>91848</v>
+        <v>79260</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -983,19 +974,23 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1003,10 +998,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>458981</v>
+        <v>459006</v>
       </c>
       <c r="R5" t="n">
-        <v>7080328</v>
+        <v>7080327</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1039,6 +1034,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 61045-2025 artfynd.xlsx
+++ b/artfynd/A 61045-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131389079</v>
+        <v>131389092</v>
       </c>
       <c r="B2" t="n">
-        <v>91848</v>
+        <v>79260</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,19 +686,23 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -706,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>459042</v>
+        <v>459047</v>
       </c>
       <c r="R2" t="n">
-        <v>7080319</v>
+        <v>7080320</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -742,6 +746,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -768,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131389092</v>
+        <v>131389079</v>
       </c>
       <c r="B3" t="n">
-        <v>79260</v>
+        <v>91848</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -779,23 +788,19 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -803,10 +808,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>459047</v>
+        <v>459042</v>
       </c>
       <c r="R3" t="n">
-        <v>7080320</v>
+        <v>7080319</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -839,11 +844,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2026-02-27</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -870,10 +870,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131389080</v>
+        <v>131389095</v>
       </c>
       <c r="B4" t="n">
-        <v>91848</v>
+        <v>79260</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -881,19 +881,23 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -901,10 +905,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>458981</v>
+        <v>459006</v>
       </c>
       <c r="R4" t="n">
-        <v>7080328</v>
+        <v>7080327</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -937,6 +941,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -963,10 +972,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131389095</v>
+        <v>131389080</v>
       </c>
       <c r="B5" t="n">
-        <v>79260</v>
+        <v>91848</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -974,23 +983,19 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -998,10 +1003,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>459006</v>
+        <v>458981</v>
       </c>
       <c r="R5" t="n">
-        <v>7080327</v>
+        <v>7080328</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1034,11 +1039,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2026-02-27</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 61045-2025 artfynd.xlsx
+++ b/artfynd/A 61045-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131389092</v>
       </c>
       <c r="B2" t="n">
-        <v>79260</v>
+        <v>79261</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>131389079</v>
       </c>
       <c r="B3" t="n">
-        <v>91848</v>
+        <v>91849</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -870,10 +870,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131389095</v>
+        <v>131389080</v>
       </c>
       <c r="B4" t="n">
-        <v>79260</v>
+        <v>91849</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -881,23 +881,19 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -905,10 +901,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>459006</v>
+        <v>458981</v>
       </c>
       <c r="R4" t="n">
-        <v>7080327</v>
+        <v>7080328</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -941,11 +937,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2026-02-27</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -972,10 +963,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131389080</v>
+        <v>131389095</v>
       </c>
       <c r="B5" t="n">
-        <v>91848</v>
+        <v>79261</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -983,19 +974,23 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1003,10 +998,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>458981</v>
+        <v>459006</v>
       </c>
       <c r="R5" t="n">
-        <v>7080328</v>
+        <v>7080327</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1039,6 +1034,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1068,7 +1068,7 @@
         <v>131389093</v>
       </c>
       <c r="B6" t="n">
-        <v>79260</v>
+        <v>79261</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1170,7 +1170,7 @@
         <v>131389094</v>
       </c>
       <c r="B7" t="n">
-        <v>79260</v>
+        <v>79261</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1272,7 +1272,7 @@
         <v>131389078</v>
       </c>
       <c r="B8" t="n">
-        <v>91848</v>
+        <v>91849</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 61045-2025 artfynd.xlsx
+++ b/artfynd/A 61045-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131389092</v>
       </c>
       <c r="B2" t="n">
-        <v>79261</v>
+        <v>79264</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>131389079</v>
       </c>
       <c r="B3" t="n">
-        <v>91849</v>
+        <v>91852</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -870,10 +870,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131389080</v>
+        <v>131389095</v>
       </c>
       <c r="B4" t="n">
-        <v>91849</v>
+        <v>79264</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -881,19 +881,23 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -901,10 +905,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>458981</v>
+        <v>459006</v>
       </c>
       <c r="R4" t="n">
-        <v>7080328</v>
+        <v>7080327</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -937,6 +941,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -963,10 +972,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131389095</v>
+        <v>131389080</v>
       </c>
       <c r="B5" t="n">
-        <v>79261</v>
+        <v>91852</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -974,23 +983,19 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -998,10 +1003,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>459006</v>
+        <v>458981</v>
       </c>
       <c r="R5" t="n">
-        <v>7080327</v>
+        <v>7080328</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1034,11 +1039,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2026-02-27</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1068,7 +1068,7 @@
         <v>131389093</v>
       </c>
       <c r="B6" t="n">
-        <v>79261</v>
+        <v>79264</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1170,7 +1170,7 @@
         <v>131389094</v>
       </c>
       <c r="B7" t="n">
-        <v>79261</v>
+        <v>79264</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1272,7 +1272,7 @@
         <v>131389078</v>
       </c>
       <c r="B8" t="n">
-        <v>91849</v>
+        <v>91852</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 61045-2025 artfynd.xlsx
+++ b/artfynd/A 61045-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,30 +675,34 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131389079</v>
+        <v>131389092</v>
       </c>
       <c r="B2" t="n">
-        <v>91858</v>
+        <v>79327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -706,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>459042</v>
+        <v>459047</v>
       </c>
       <c r="R2" t="n">
-        <v>7080319</v>
+        <v>7080320</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -742,6 +746,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -768,14 +777,14 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131389092</v>
+        <v>131389093</v>
       </c>
       <c r="B3" t="n">
-        <v>79266</v>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -803,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>459047</v>
+        <v>459020</v>
       </c>
       <c r="R3" t="n">
-        <v>7080320</v>
+        <v>7080190</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -843,7 +852,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Mycket rikligt</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -870,30 +879,34 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131389080</v>
+        <v>131389094</v>
       </c>
       <c r="B4" t="n">
-        <v>91858</v>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -901,10 +914,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>458981</v>
+        <v>459168</v>
       </c>
       <c r="R4" t="n">
-        <v>7080328</v>
+        <v>7080241</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -937,6 +950,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -966,11 +984,11 @@
         <v>131389095</v>
       </c>
       <c r="B5" t="n">
-        <v>79266</v>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -1062,303 +1080,6 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>131389093</v>
-      </c>
-      <c r="B6" t="n">
-        <v>79266</v>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>Tretjärnrun, Jmt</t>
-        </is>
-      </c>
-      <c r="Q6" t="n">
-        <v>459020</v>
-      </c>
-      <c r="R6" t="n">
-        <v>7080190</v>
-      </c>
-      <c r="S6" t="n">
-        <v>10</v>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>Föllinge</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>2026-02-27</t>
-        </is>
-      </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>2026-02-27</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
-        </is>
-      </c>
-      <c r="AD6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT6" t="inlineStr"/>
-      <c r="AW6" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>131389094</v>
-      </c>
-      <c r="B7" t="n">
-        <v>79266</v>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>Tretjärnrun, Jmt</t>
-        </is>
-      </c>
-      <c r="Q7" t="n">
-        <v>459168</v>
-      </c>
-      <c r="R7" t="n">
-        <v>7080241</v>
-      </c>
-      <c r="S7" t="n">
-        <v>10</v>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>Föllinge</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>2026-02-27</t>
-        </is>
-      </c>
-      <c r="AA7" t="inlineStr">
-        <is>
-          <t>2026-02-27</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Mycket rikligt</t>
-        </is>
-      </c>
-      <c r="AD7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT7" t="inlineStr"/>
-      <c r="AW7" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>131389078</v>
-      </c>
-      <c r="B8" t="n">
-        <v>91858</v>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>5432</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Granticka</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>Tretjärnrun, Jmt</t>
-        </is>
-      </c>
-      <c r="Q8" t="n">
-        <v>459129</v>
-      </c>
-      <c r="R8" t="n">
-        <v>7080272</v>
-      </c>
-      <c r="S8" t="n">
-        <v>10</v>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>Föllinge</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>2026-02-27</t>
-        </is>
-      </c>
-      <c r="AA8" t="inlineStr">
-        <is>
-          <t>2026-02-27</t>
-        </is>
-      </c>
-      <c r="AD8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT8" t="inlineStr"/>
-      <c r="AW8" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
